--- a/output/rss_history_2.xlsx
+++ b/output/rss_history_2.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1311"/>
+  <dimension ref="A1:E1312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35659,6 +35659,29 @@
       <c r="E1311" t="inlineStr">
         <is>
           <t>NON_CLASSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>Frandroid - Actualités</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr"/>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>À partir de 599 €, ces nouveaux robots aspirateurs ECOVACS lavent le sol avec un rouleau</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4238</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -38158,7 +38181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38580,6 +38603,29 @@
         </is>
       </c>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>11. Menage</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Frandroid - Actualités</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>À partir de 599 €, ces nouveaux robots aspirateurs ECOVACS lavent le sol avec un rouleau</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4238</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>11. Menage</t>
         </is>
